--- a/Starfront/文档/配置表/GMResource.xlsx
+++ b/Starfront/文档/配置表/GMResource.xlsx
@@ -1021,311 +1021,321 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F18"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="20.25"/>
-  <cols>
-    <col width="9" customWidth="1" style="3" min="1" max="2"/>
-    <col width="22" customWidth="1" style="3" min="3" max="3"/>
-    <col width="21" customWidth="1" style="3" min="4" max="4"/>
-    <col width="18.77499961853027" customWidth="1" style="2" min="5" max="5"/>
-    <col width="21.5" customWidth="1" style="2" min="6" max="6"/>
-    <col width="9" customWidth="1" style="3" min="7" max="16384"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customFormat="1" customHeight="1" s="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>##var</t>
-        </is>
-      </c>
-      <c r="B1" s="5" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="C1" s="5" t="inlineStr">
-        <is>
-          <t>desc</t>
-        </is>
-      </c>
-      <c r="D1" s="5" t="inlineStr">
-        <is>
-          <t>content</t>
-        </is>
-      </c>
-      <c r="E1" s="5" t="inlineStr">
-        <is>
-          <t>paramFormat</t>
-        </is>
-      </c>
-      <c r="F1" s="5" t="inlineStr">
-        <is>
-          <t>paramIntro</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" customFormat="1" s="2">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>##</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="n"/>
-      <c r="C2" s="7" t="inlineStr">
-        <is>
-          <t>描述</t>
-        </is>
-      </c>
-      <c r="D2" s="7" t="inlineStr">
-        <is>
-          <t>名称</t>
-        </is>
-      </c>
-      <c r="E2" s="7" t="inlineStr">
-        <is>
-          <t>参数</t>
-        </is>
-      </c>
-      <c r="F2" s="7" t="inlineStr">
-        <is>
-          <t>参数说明</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" customFormat="1" s="2">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>##type</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>(list#sep=,),string</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>(list#sep=,),string</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="8" t="n"/>
-      <c r="B4" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>输出调试日志</t>
-        </is>
-      </c>
-      <c r="D4" s="8" t="inlineStr">
-        <is>
-          <t>log</t>
-        </is>
-      </c>
-      <c r="E4" s="9" t="inlineStr">
-        <is>
-          <t>GM ready</t>
-        </is>
-      </c>
-      <c r="F4" s="9" t="inlineStr">
-        <is>
-          <t>日志内容</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="8" t="n"/>
-      <c r="B5" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>设置场景时间倍率</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>timeScale</t>
-        </is>
-      </c>
-      <c r="E5" s="9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F5" s="9" t="inlineStr">
-        <is>
-          <t>大于0的倍率</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="8" t="n"/>
-      <c r="B6" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>暂停场景计时器</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>timePause</t>
-        </is>
-      </c>
-      <c r="E6" s="9" t="n"/>
-      <c r="F6" s="9" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="8" t="n"/>
-      <c r="B7" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>恢复场景计时器</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>timeResume</t>
-        </is>
-      </c>
-      <c r="E7" s="9" t="n"/>
-      <c r="F7" s="9" t="n"/>
-    </row>
-    <row r="8" s="10">
-      <c r="A8" s="8" t="n"/>
-      <c r="B8" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>关闭GM面板</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>closeGM</t>
-        </is>
-      </c>
-      <c r="E8" s="9" t="n"/>
-      <c r="F8" s="9" t="n"/>
-    </row>
-    <row r="9" s="10">
-      <c r="A9" s="8" t="n"/>
-      <c r="B9" s="8" t="n">
-        <v>1001</v>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>打开图层效果测试界面</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>openLayerEffectTest</t>
-        </is>
-      </c>
-      <c r="E9" s="9" t="n"/>
-      <c r="F9" s="9" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="8" t="n"/>
-      <c r="B10" s="8" t="n"/>
-      <c r="C10" s="8" t="n"/>
-      <c r="D10" s="8" t="n"/>
-      <c r="E10" s="9" t="n"/>
-      <c r="F10" s="9" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="8" t="n"/>
-      <c r="B11" s="8" t="n"/>
-      <c r="C11" s="8" t="n"/>
-      <c r="D11" s="8" t="n"/>
-      <c r="E11" s="9" t="n"/>
-      <c r="F11" s="9" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="8" t="n"/>
-      <c r="B12" s="8" t="n"/>
-      <c r="C12" s="8" t="n"/>
-      <c r="D12" s="8" t="n"/>
-      <c r="E12" s="9" t="n"/>
-      <c r="F12" s="9" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="8" t="n"/>
-      <c r="B13" s="8" t="n"/>
-      <c r="C13" s="8" t="n"/>
-      <c r="D13" s="8" t="n"/>
-      <c r="E13" s="9" t="n"/>
-      <c r="F13" s="9" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="8" t="n"/>
-      <c r="B14" s="8" t="n"/>
-      <c r="C14" s="8" t="n"/>
-      <c r="D14" s="8" t="n"/>
-      <c r="E14" s="9" t="n"/>
-      <c r="F14" s="9" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="8" t="n"/>
-      <c r="B15" s="8" t="n"/>
-      <c r="C15" s="8" t="n"/>
-      <c r="D15" s="8" t="n"/>
-      <c r="E15" s="9" t="n"/>
-      <c r="F15" s="9" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="8" t="n"/>
-      <c r="B16" s="8" t="n"/>
-      <c r="C16" s="8" t="n"/>
-      <c r="D16" s="8" t="n"/>
-      <c r="E16" s="9" t="n"/>
-      <c r="F16" s="9" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="8" t="n"/>
-      <c r="B17" s="8" t="n"/>
-      <c r="C17" s="8" t="n"/>
-      <c r="D17" s="8" t="n"/>
-      <c r="E17" s="9" t="n"/>
-      <c r="F17" s="9" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="8" t="n"/>
-      <c r="B18" s="8" t="n"/>
-      <c r="C18" s="8" t="n"/>
-      <c r="D18" s="8" t="n"/>
-      <c r="E18" s="9" t="n"/>
-      <c r="F18" s="9" t="n"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
+<ns0:worksheet xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <ns0:sheetPr>
+    <ns0:outlinePr summaryBelow="1" summaryRight="1"/>
+    <ns0:pageSetUpPr/>
+  </ns0:sheetPr>
+  <ns0:dimension ref="A1:F18"/>
+  <ns0:sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="20.25"/>
+  <ns0:cols>
+    <ns0:col width="9" customWidth="1" style="3" min="1" max="2"/>
+    <ns0:col width="22" customWidth="1" style="3" min="3" max="3"/>
+    <ns0:col width="21" customWidth="1" style="3" min="4" max="4"/>
+    <ns0:col width="18.77499961853027" customWidth="1" style="2" min="5" max="5"/>
+    <ns0:col width="21.5" customWidth="1" style="2" min="6" max="6"/>
+    <ns0:col width="9" customWidth="1" style="3" min="7" max="16384"/>
+  </ns0:cols>
+  <ns0:sheetData>
+    <ns0:row r="1" ht="30" customFormat="1" customHeight="1" s="1">
+      <ns0:c r="A1" s="4" t="inlineStr">
+        <ns0:is>
+          <ns0:t>##var</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B1" s="5" t="inlineStr">
+        <ns0:is>
+          <ns0:t>id</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C1" s="5" t="inlineStr">
+        <ns0:is>
+          <ns0:t>desc</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D1" s="5" t="inlineStr">
+        <ns0:is>
+          <ns0:t>content</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E1" s="5" t="inlineStr">
+        <ns0:is>
+          <ns0:t>paramFormat</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F1" s="5" t="inlineStr">
+        <ns0:is>
+          <ns0:t>paramIntro</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="2" customFormat="1" s="2">
+      <ns0:c r="A2" s="6" t="inlineStr">
+        <ns0:is>
+          <ns0:t>##</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B2" s="7" t="n"/>
+      <ns0:c r="C2" s="7" t="inlineStr">
+        <ns0:is>
+          <ns0:t>描述</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D2" s="7" t="inlineStr">
+        <ns0:is>
+          <ns0:t>名称</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E2" s="7" t="inlineStr">
+        <ns0:is>
+          <ns0:t>参数</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F2" s="7" t="inlineStr">
+        <ns0:is>
+          <ns0:t>参数说明</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="3" customFormat="1" s="2">
+      <ns0:c r="A3" s="4" t="inlineStr">
+        <ns0:is>
+          <ns0:t>##type</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B3" s="5" t="inlineStr">
+        <ns0:is>
+          <ns0:t>int</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C3" s="5" t="inlineStr">
+        <ns0:is>
+          <ns0:t>string</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D3" s="5" t="inlineStr">
+        <ns0:is>
+          <ns0:t>string</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E3" s="5" t="inlineStr">
+        <ns0:is>
+          <ns0:t>(list#sep=,),string</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F3" s="5" t="inlineStr">
+        <ns0:is>
+          <ns0:t>(list#sep=,),string</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="4">
+      <ns0:c r="A4" s="8" t="n"/>
+      <ns0:c r="B4" s="8" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="C4" s="8" t="inlineStr">
+        <ns0:is>
+          <ns0:t>输出调试日志</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D4" s="8" t="inlineStr">
+        <ns0:is>
+          <ns0:t>log</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E4" s="9" t="inlineStr">
+        <ns0:is>
+          <ns0:t>GM ready</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F4" s="9" t="inlineStr">
+        <ns0:is>
+          <ns0:t>日志内容</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="5">
+      <ns0:c r="A5" s="8" t="n"/>
+      <ns0:c r="B5" s="8" t="n">
+        <ns0:v>2</ns0:v>
+      </ns0:c>
+      <ns0:c r="C5" s="8" t="inlineStr">
+        <ns0:is>
+          <ns0:t>设置场景时间倍率</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D5" s="8" t="inlineStr">
+        <ns0:is>
+          <ns0:t>timeScale</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E5" s="9" t="inlineStr">
+        <ns0:is>
+          <ns0:t>1</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F5" s="9" t="inlineStr">
+        <ns0:is>
+          <ns0:t>大于0的倍率</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="6">
+      <ns0:c r="A6" s="8" t="n"/>
+      <ns0:c r="B6" s="8" t="n">
+        <ns0:v>3</ns0:v>
+      </ns0:c>
+      <ns0:c r="C6" s="8" t="inlineStr">
+        <ns0:is>
+          <ns0:t>暂停场景计时器</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D6" s="8" t="inlineStr">
+        <ns0:is>
+          <ns0:t>timePause</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E6" s="9" t="n"/>
+      <ns0:c r="F6" s="9" t="n"/>
+    </ns0:row>
+    <ns0:row r="7">
+      <ns0:c r="A7" s="8" t="n"/>
+      <ns0:c r="B7" s="8" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
+      <ns0:c r="C7" s="8" t="inlineStr">
+        <ns0:is>
+          <ns0:t>恢复场景计时器</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D7" s="8" t="inlineStr">
+        <ns0:is>
+          <ns0:t>timeResume</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E7" s="9" t="n"/>
+      <ns0:c r="F7" s="9" t="n"/>
+    </ns0:row>
+    <ns0:row r="8" s="10">
+      <ns0:c r="A8" s="8" t="n"/>
+      <ns0:c r="B8" s="8" t="n">
+        <ns0:v>5</ns0:v>
+      </ns0:c>
+      <ns0:c r="C8" s="8" t="inlineStr">
+        <ns0:is>
+          <ns0:t>关闭GM面板</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D8" s="8" t="inlineStr">
+        <ns0:is>
+          <ns0:t>closeGM</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E8" s="9" t="n"/>
+      <ns0:c r="F8" s="9" t="n"/>
+    </ns0:row>
+    <ns0:row r="9" s="10">
+      <ns0:c r="A9" s="8" t="n"/>
+      <ns0:c r="B9" s="8" t="n">
+        <ns0:v>1001</ns0:v>
+      </ns0:c>
+      <ns0:c r="C9" s="8" t="inlineStr">
+        <ns0:is>
+          <ns0:t>打开图层效果测试界面</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D9" s="8" t="inlineStr">
+        <ns0:is>
+          <ns0:t>openLayerEffectTest</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E9" s="9" t="n"/>
+      <ns0:c r="F9" s="9" t="n"/>
+    </ns0:row>
+    <ns0:row r="10">
+      <ns0:c r="A10" s="8" t="n"/>
+      <ns0:c r="B10" s="8" t="n">
+        <ns0:v>1002</ns0:v>
+      </ns0:c>
+      <ns0:c r="C10" s="8" t="str">
+        <ns0:v>测试当前单位离地高度</ns0:v>
+      </ns0:c>
+      <ns0:c r="D10" s="8" t="str">
+        <ns0:v>unitAltitude</ns0:v>
+      </ns0:c>
+      <ns0:c r="E10" s="9" t="str">
+        <ns0:v>40</ns0:v>
+      </ns0:c>
+      <ns0:c r="F10" s="9" t="str">
+        <ns0:v>离地高度（场景像素，0恢复贴地）</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="11">
+      <ns0:c r="A11" s="8" t="n"/>
+      <ns0:c r="B11" s="8" t="n"/>
+      <ns0:c r="C11" s="8" t="n"/>
+      <ns0:c r="D11" s="8" t="n"/>
+      <ns0:c r="E11" s="9" t="n"/>
+      <ns0:c r="F11" s="9" t="n"/>
+    </ns0:row>
+    <ns0:row r="12">
+      <ns0:c r="A12" s="8" t="n"/>
+      <ns0:c r="B12" s="8" t="n"/>
+      <ns0:c r="C12" s="8" t="n"/>
+      <ns0:c r="D12" s="8" t="n"/>
+      <ns0:c r="E12" s="9" t="n"/>
+      <ns0:c r="F12" s="9" t="n"/>
+    </ns0:row>
+    <ns0:row r="13">
+      <ns0:c r="A13" s="8" t="n"/>
+      <ns0:c r="B13" s="8" t="n"/>
+      <ns0:c r="C13" s="8" t="n"/>
+      <ns0:c r="D13" s="8" t="n"/>
+      <ns0:c r="E13" s="9" t="n"/>
+      <ns0:c r="F13" s="9" t="n"/>
+    </ns0:row>
+    <ns0:row r="14">
+      <ns0:c r="A14" s="8" t="n"/>
+      <ns0:c r="B14" s="8" t="n"/>
+      <ns0:c r="C14" s="8" t="n"/>
+      <ns0:c r="D14" s="8" t="n"/>
+      <ns0:c r="E14" s="9" t="n"/>
+      <ns0:c r="F14" s="9" t="n"/>
+    </ns0:row>
+    <ns0:row r="15">
+      <ns0:c r="A15" s="8" t="n"/>
+      <ns0:c r="B15" s="8" t="n"/>
+      <ns0:c r="C15" s="8" t="n"/>
+      <ns0:c r="D15" s="8" t="n"/>
+      <ns0:c r="E15" s="9" t="n"/>
+      <ns0:c r="F15" s="9" t="n"/>
+    </ns0:row>
+    <ns0:row r="16">
+      <ns0:c r="A16" s="8" t="n"/>
+      <ns0:c r="B16" s="8" t="n"/>
+      <ns0:c r="C16" s="8" t="n"/>
+      <ns0:c r="D16" s="8" t="n"/>
+      <ns0:c r="E16" s="9" t="n"/>
+      <ns0:c r="F16" s="9" t="n"/>
+    </ns0:row>
+    <ns0:row r="17">
+      <ns0:c r="A17" s="8" t="n"/>
+      <ns0:c r="B17" s="8" t="n"/>
+      <ns0:c r="C17" s="8" t="n"/>
+      <ns0:c r="D17" s="8" t="n"/>
+      <ns0:c r="E17" s="9" t="n"/>
+      <ns0:c r="F17" s="9" t="n"/>
+    </ns0:row>
+    <ns0:row r="18">
+      <ns0:c r="A18" s="8" t="n"/>
+      <ns0:c r="B18" s="8" t="n"/>
+      <ns0:c r="C18" s="8" t="n"/>
+      <ns0:c r="D18" s="8" t="n"/>
+      <ns0:c r="E18" s="9" t="n"/>
+      <ns0:c r="F18" s="9" t="n"/>
+    </ns0:row>
+  </ns0:sheetData>
+  <ns0:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</ns0:worksheet>
 </file>